--- a/RobotData.xlsx
+++ b/RobotData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\GitHub\robotics-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jim Goodall\Documents\Robotics\Controls\robotics-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78521198-CC81-4F80-8C0D-9E4979B2F5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEA4726-95FF-4B18-8C08-66067BDC3A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{FC88B133-5631-431F-8B38-05BF9FDD5FAD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{FC88B133-5631-431F-8B38-05BF9FDD5FAD}"/>
   </bookViews>
   <sheets>
     <sheet name="AngleFunction" sheetId="20" r:id="rId1"/>
@@ -22,9 +22,6 @@
     <sheet name="Shooting" sheetId="22" r:id="rId7"/>
     <sheet name="ShootSpeed" sheetId="27" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Calibration!$A$24:$J$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Shooting!$A$17:$S$331</definedName>
@@ -50,7 +47,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -72,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="113">
   <si>
     <t>d</t>
   </si>
@@ -393,10 +390,6 @@
     <t>Left STDEV</t>
   </si>
   <si>
-    <t>Time
-s</t>
-  </si>
-  <si>
     <t>Balls Loaded
 count</t>
   </si>
@@ -412,12 +405,14 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Balls Delivered
+    <t>Jams
 count</t>
   </si>
   <si>
-    <t>Jams
-count</t>
+    <t>Seconds to balls</t>
+  </si>
+  <si>
+    <t>just no</t>
   </si>
 </sst>
 </file>
@@ -838,13 +833,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -882,9 +871,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="8" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -936,6 +922,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="8" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -25239,67 +25234,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Lag Filter"/>
-      <sheetName val="Fuel Fill Calc"/>
-      <sheetName val="RVP TVP Calc"/>
-      <sheetName val="Altitude"/>
-      <sheetName val="Std Dev"/>
-      <sheetName val="Interpolate"/>
-      <sheetName val="Discrete Stats"/>
-      <sheetName val="Continuous Stats"/>
-      <sheetName val="Temp Pressure"/>
-      <sheetName val="Units"/>
-      <sheetName val="Phonetics"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5">
-        <row r="4">
-          <cell r="B4">
-            <v>96</v>
-          </cell>
-          <cell r="C4">
-            <v>400</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6">
-            <v>100</v>
-          </cell>
-          <cell r="C6">
-            <v>412.5</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8">
-            <v>104</v>
-          </cell>
-          <cell r="C8">
-            <v>425</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -51734,290 +51668,290 @@
   </cols>
   <sheetData>
     <row r="2" spans="8:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="20" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
     </row>
     <row r="23" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="23"/>
-      <c r="C23" s="24" t="s">
+      <c r="B23" s="21"/>
+      <c r="C23" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="23">
         <v>100</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="23">
         <v>1000</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="23">
         <v>10000</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="23">
         <v>100000</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="23">
         <v>1000000</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="23">
         <v>10000000</v>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="23">
         <v>100000000</v>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="23">
         <v>1000000000</v>
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="25">
         <v>0.68268949213700003</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="25">
         <f>100%-C24</f>
         <v>0.31731050786299997</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="26">
         <f>$D24*E$23</f>
         <v>31.731050786299996</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="26">
         <f t="shared" ref="F24:L28" si="0">$D24*F$23</f>
         <v>317.31050786299994</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="26">
         <f t="shared" si="0"/>
         <v>3173.1050786299998</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="26">
         <f t="shared" si="0"/>
         <v>31731.050786299998</v>
       </c>
-      <c r="I24" s="28">
+      <c r="I24" s="26">
         <f t="shared" si="0"/>
         <v>317310.50786299998</v>
       </c>
-      <c r="J24" s="28">
+      <c r="J24" s="26">
         <f>$D24*J$23</f>
         <v>3173105.0786299999</v>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="26">
         <f t="shared" si="0"/>
         <v>31731050.786299996</v>
       </c>
-      <c r="L24" s="28">
+      <c r="L24" s="26">
         <f t="shared" si="0"/>
         <v>317310507.86299998</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="25">
         <v>0.95449973610399996</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="25">
         <f>100%-C25</f>
         <v>4.5500263896000037E-2</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="26">
         <f>$D25*E$23</f>
         <v>4.5500263896000037</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="26">
         <f t="shared" si="0"/>
         <v>45.500263896000035</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="26">
         <f t="shared" si="0"/>
         <v>455.00263896000035</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="26">
         <f t="shared" si="0"/>
         <v>4550.0263896000033</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="26">
         <f t="shared" si="0"/>
         <v>45500.26389600004</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="26">
         <f>$D25*J$23</f>
         <v>455002.63896000036</v>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="26">
         <f t="shared" si="0"/>
         <v>4550026.3896000041</v>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="26">
         <f t="shared" si="0"/>
         <v>45500263.896000035</v>
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="25">
         <v>0.99730020393700003</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="25">
         <f>100%-C26</f>
         <v>2.6997960629999707E-3</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="28">
+      <c r="E26" s="28"/>
+      <c r="F26" s="26">
         <f>$D26*F$23</f>
         <v>2.6997960629999707</v>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="26">
         <f t="shared" si="0"/>
         <v>26.997960629999707</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H26" s="26">
         <f t="shared" si="0"/>
         <v>269.97960629999704</v>
       </c>
-      <c r="I26" s="28">
+      <c r="I26" s="26">
         <f t="shared" si="0"/>
         <v>2699.7960629999707</v>
       </c>
-      <c r="J26" s="28">
+      <c r="J26" s="26">
         <f>$D26*J$23</f>
         <v>26997.960629999707</v>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="26">
         <f t="shared" si="0"/>
         <v>269979.60629999707</v>
       </c>
-      <c r="L26" s="28">
+      <c r="L26" s="26">
         <f t="shared" si="0"/>
         <v>2699796.0629999707</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="29">
         <v>0.99993665751600003</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="29">
         <f t="shared" ref="D27:D29" si="1">100%-C27</f>
         <v>6.3342483999972998E-5</v>
       </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="28">
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="26">
         <f>$D27*G$23</f>
         <v>0.63342483999972998</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="26">
         <f>$D27*H$23</f>
         <v>6.3342483999972998</v>
       </c>
-      <c r="I27" s="28">
+      <c r="I27" s="26">
         <f>$D27*I$23</f>
         <v>63.342483999972998</v>
       </c>
-      <c r="J27" s="28">
+      <c r="J27" s="26">
         <f>$D27*J$23</f>
         <v>633.42483999973001</v>
       </c>
-      <c r="K27" s="28">
+      <c r="K27" s="26">
         <f t="shared" si="0"/>
         <v>6334.2483999973001</v>
       </c>
-      <c r="L27" s="28">
+      <c r="L27" s="26">
         <f t="shared" si="0"/>
         <v>63342.483999972996</v>
       </c>
     </row>
     <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="30">
         <v>0.99999942669700004</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="30">
         <f t="shared" si="1"/>
         <v>5.7330299996216638E-7</v>
       </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="28">
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="26">
         <f>$D28*I$23</f>
         <v>0.57330299996216638</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="26">
         <f>$D28*J$23</f>
         <v>5.7330299996216638</v>
       </c>
-      <c r="K28" s="28">
+      <c r="K28" s="26">
         <f t="shared" si="0"/>
         <v>57.330299996216638</v>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="26">
         <f t="shared" si="0"/>
         <v>573.30299996216638</v>
       </c>
     </row>
     <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="31">
         <v>0.99999999802700001</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="31">
         <f t="shared" si="1"/>
         <v>1.972999985611068E-9</v>
       </c>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="28">
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="26">
         <f>$D29*L$23</f>
         <v>1.972999985611068</v>
       </c>
     </row>
     <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="34"/>
+      <c r="C30" s="32"/>
     </row>
     <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="35"/>
-      <c r="C31" s="34"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="32"/>
     </row>
     <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C32" s="34"/>
+      <c r="C32" s="32"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="35"/>
-      <c r="C33" s="34"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -52037,7 +51971,7 @@
   <cols>
     <col min="2" max="2" width="20.140625" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="45" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="42" customWidth="1"/>
     <col min="8" max="8" width="23.28515625" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" customWidth="1"/>
     <col min="10" max="10" width="6.7109375" customWidth="1"/>
@@ -52046,18 +51980,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="H2" s="36" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="H2" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
     </row>
     <row r="3" spans="2:13" ht="9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C3"/>
@@ -52070,13 +52004,13 @@
       <c r="C4" s="3">
         <v>48</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="41" t="s">
         <v>78</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="34">
         <v>0.5</v>
       </c>
       <c r="K4" s="6" t="s">
@@ -52090,7 +52024,7 @@
       <c r="C5" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="41">
         <f>BINOMDIST(C6,C4,C5,C7)</f>
         <v>0.12503595996144101</v>
       </c>
@@ -52100,7 +52034,7 @@
       <c r="I5" s="8">
         <v>0.14777000000000001</v>
       </c>
-      <c r="K5" s="38">
+      <c r="K5" s="35">
         <f>CEILING(((NORMSINV(1-(1-I4)/2)*I6)/I5)^2,1)</f>
         <v>31</v>
       </c>
@@ -52129,23 +52063,23 @@
     </row>
     <row r="8" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="36" t="s">
+      <c r="B10" s="55" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="H10" s="36" t="s">
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="H10" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
     </row>
     <row r="11" spans="2:13" ht="9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="46"/>
+      <c r="B11" s="43"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
@@ -52154,13 +52088,13 @@
       <c r="C12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="41" t="s">
         <v>78</v>
       </c>
       <c r="H12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="34">
         <v>0.5</v>
       </c>
       <c r="K12" s="6" t="s">
@@ -52180,7 +52114,7 @@
       <c r="C13" s="3">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="41">
         <f>POISSON(C12,C13,C14)</f>
         <v>0.10025884372280375</v>
       </c>
@@ -52194,11 +52128,11 @@
         <f>_xlfn.CONFIDENCE.NORM(1-I12,I14,I15)</f>
         <v>0.14777330039536743</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="37">
         <f>I13-K13</f>
         <v>4.8522266996046328</v>
       </c>
-      <c r="M13" s="40">
+      <c r="M13" s="37">
         <f>I13+K13</f>
         <v>5.1477733003953672</v>
       </c>
@@ -52221,26 +52155,26 @@
       <c r="H15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="38">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="H17" s="36" t="s">
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="H17" s="55" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
     </row>
     <row r="18" spans="2:11" ht="9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="46"/>
+      <c r="B18" s="43"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
@@ -52249,13 +52183,13 @@
       <c r="C19" s="3">
         <v>1</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="41" t="s">
         <v>78</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="34">
         <v>0.9</v>
       </c>
       <c r="K19" s="6" t="s">
@@ -52269,7 +52203,7 @@
       <c r="C20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="41">
         <f>HYPGEOMDIST(C19,C20,C21,C22)</f>
         <v>0.3611974841430648</v>
       </c>
@@ -52279,7 +52213,7 @@
       <c r="I20" s="8">
         <v>16</v>
       </c>
-      <c r="K20" s="42" t="str">
+      <c r="K20" s="39" t="str">
         <f>ROUND(I20/I21,3)&amp;" ± "&amp;ROUND(NORMSINV(1-(1-I19)/2)*SQRT((I20/I21)*(1-(I20/I21))/I21),3)</f>
         <v>0.16 ± 0.06</v>
       </c>
@@ -52294,7 +52228,7 @@
       <c r="H21" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="38">
         <v>100</v>
       </c>
     </row>
@@ -52307,12 +52241,12 @@
       </c>
     </row>
     <row r="24" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -52322,7 +52256,7 @@
       <c r="C26" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="E26" s="44" t="s">
+      <c r="E26" s="41" t="s">
         <v>78</v>
       </c>
     </row>
@@ -52333,7 +52267,7 @@
       <c r="C27" s="3">
         <v>48</v>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="44">
         <f>1-(1-C26)^C27</f>
         <v>0.1342996383225229</v>
       </c>
@@ -52363,23 +52297,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="7" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
     </row>
     <row r="2" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="46" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="46" t="s">
         <v>96</v>
       </c>
       <c r="B4" s="3">
@@ -52390,25 +52324,25 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
+      <c r="A5" s="46"/>
     </row>
     <row r="6" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="46" t="s">
         <v>97</v>
       </c>
       <c r="B6" s="3">
         <v>100</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="47">
         <f>C4+(C8-C4)*((B6-B4)/(B8-B4))</f>
         <v>412.5</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
+      <c r="A7" s="46"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="46" t="s">
         <v>98</v>
       </c>
       <c r="B8" s="3">
@@ -52419,7 +52353,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
+      <c r="A9" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52636,17 +52570,17 @@
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="56"/>
+      <c r="I23" s="56"/>
     </row>
     <row r="24" spans="1:9" s="14" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -53669,7 +53603,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="48" t="s">
         <v>99</v>
       </c>
       <c r="B1" s="10"/>
@@ -63343,57 +63277,665 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BEDA8AB-35F7-4B90-BA2D-354C8BB5D259}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="4" customWidth="1"/>
-    <col min="2" max="5" width="9.140625" style="4"/>
-    <col min="6" max="7" width="9.140625" style="3"/>
-    <col min="8" max="8" width="37.42578125" style="56" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="43"/>
+    <col min="1" max="4" width="9.140625" style="4"/>
+    <col min="5" max="6" width="9.140625" style="3"/>
+    <col min="7" max="7" width="37.42578125" style="53" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+    <row r="1" spans="1:7" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="D1" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="53" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="54" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7.95</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="E3" s="3">
+        <v>10.09</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="E4" s="3">
+        <v>12.03</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="E5" s="3">
+        <v>14.74</v>
+      </c>
+      <c r="F5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="E6" s="3">
+        <v>13.07</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <v>12.7</v>
+      </c>
+      <c r="E7" s="3">
+        <v>9.42</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6.92</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5.65</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5.76</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>12.6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>7.78</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>8</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6.93</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>6.08</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8.02</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>8</v>
+      </c>
+      <c r="B18" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>6.43</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>8</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>11.79</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>8</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E21" s="3">
+        <v>11.83</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>8</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>9.39</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>8</v>
+      </c>
+      <c r="B23" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>13.18</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1</v>
+      </c>
+      <c r="G23" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="H1" s="55" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>10</v>
-      </c>
-      <c r="B2" s="4">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
         <v>8</v>
       </c>
-      <c r="C2" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="B24" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C24" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="4">
-        <v>12.6</v>
+      <c r="D24" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="F24" s="3">
+        <v>2</v>
+      </c>
+      <c r="G24" s="53" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>8</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="E25" s="3">
+        <v>17.78</v>
+      </c>
+      <c r="F25" s="3">
+        <v>2</v>
+      </c>
+      <c r="G25" s="53" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>8</v>
+      </c>
+      <c r="B26" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="E26" s="3">
+        <v>10.17</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>8</v>
+      </c>
+      <c r="B27" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>8</v>
+      </c>
+      <c r="B28" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="E28" s="3">
+        <v>12.41</v>
+      </c>
+      <c r="F28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>8</v>
+      </c>
+      <c r="B29" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="E29" s="3">
+        <v>14.09</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>8</v>
+      </c>
+      <c r="B30" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="E30" s="3">
+        <v>9.89</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>8</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="E31" s="3">
+        <v>10.17</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>8</v>
+      </c>
+      <c r="B32" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>12.21</v>
+      </c>
+      <c r="F32" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/RobotData.xlsx
+++ b/RobotData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\james\Documents\GitHub\robotics-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jim Goodall\Documents\Robotics\Controls\robotics-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60E81E7-058E-45F7-89DF-D52AC258D253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729057B1-E868-4FF9-905F-14CE7DB36086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{FC88B133-5631-431F-8B38-05BF9FDD5FAD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="8" xr2:uid="{FC88B133-5631-431F-8B38-05BF9FDD5FAD}"/>
   </bookViews>
   <sheets>
     <sheet name="AngleFunction" sheetId="20" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="131">
   <si>
     <t>d</t>
   </si>
@@ -451,13 +451,25 @@
     <t>Chance of at least x balls (Continuous)</t>
   </si>
   <si>
-    <t>Chance of at least x balls (8 balls available)</t>
-  </si>
-  <si>
     <t>Speed bpm</t>
   </si>
   <si>
     <t>Min Speed bpm</t>
+  </si>
+  <si>
+    <t>Drive</t>
+  </si>
+  <si>
+    <t>Shoot</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t>Balls in Hopper</t>
+  </si>
+  <si>
+    <t>Chance of at least x balls (with hopper)</t>
   </si>
 </sst>
 </file>
@@ -469,7 +481,7 @@
     <numFmt numFmtId="165" formatCode="0.000000%"/>
     <numFmt numFmtId="166" formatCode="0.0000000%"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -826,7 +838,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -966,15 +978,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="10" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="8" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -987,11 +990,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="172" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyAlignment="1">
@@ -999,6 +1002,18 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="8" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -6085,6 +6100,15 @@
               <a:t>Successful Delivery Rate</a:t>
             </a:r>
           </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Continuous</a:t>
+            </a:r>
+          </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
@@ -6525,7 +6549,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> of Delivering 8 Balls in 12 seconds</a:t>
+              <a:t> of Delivering 8 Balls</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -6535,8 +6559,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.15213888888888885"/>
-          <c:y val="5.5555555555555552E-2"/>
+          <c:x val="0.2168649432260332"/>
+          <c:y val="5.5555432331521937E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -6629,22 +6653,22 @@
             <c:numRef>
               <c:f>'Data Summary'!$T$3:$T$7</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.2150867841099653E-2</c:v>
+                  <c:v>1.0426014367353909E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.56892161146072384</c:v>
+                  <c:v>0.56374175516638803</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.44592929414890059</c:v>
+                  <c:v>0.44895810295391736</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.25151132404853804</c:v>
+                  <c:v>0.25395736171909966</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.12287379711403668</c:v>
+                  <c:v>0.12287387076067158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6671,6 +6695,7 @@
         <c:axId val="1069573408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.30000000000000004"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -6751,7 +6776,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -7226,6 +7251,1232 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Single Shot Probability of Success</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$A$3:$A$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$F$3:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.96383905423860639</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.95254090598405416</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.92249167226534112</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.85141766323462797</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.76298326735887789</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AC6D-478D-A76B-C174C3CBBC2C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1798733647"/>
+        <c:axId val="1798726447"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1798733647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.30000000000000004"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1798726447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.1"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1798726447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0.70000000000000007"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1798733647"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Autonomous</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Chance of Delivering Successfully</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.19157714546723556"/>
+          <c:y val="0.2626910093785767"/>
+          <c:w val="0.76342497828226019"/>
+          <c:h val="0.51331654051693265"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>0.4</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$2:$T$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$3:$T$3</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.95776489564622558</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76310469259575797</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.38488812450584486</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6516268768836566E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0426014367353909E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D6A7-4E70-B359-34E971E449B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>0.5</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$2:$T$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$4:$T$4</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.99999998042874794</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99998416573569204</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99765486328282693</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.93241434778982812</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.56374175516638803</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D6A7-4E70-B359-34E971E449B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>0.6</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$2:$T$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$5:$T$5</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.99998306884080768</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.99895550363432284</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9777184389137954</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.82645031316347495</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.44895810295391736</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D6A7-4E70-B359-34E971E449B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>0.75</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$2:$T$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$6:$T$6</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.99927266981581164</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98686384629681678</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.89629977543798078</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.61765541546167335</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25395736171909966</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D6A7-4E70-B359-34E971E449B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$2:$T$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Data Summary'!$P$7:$T$7</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.98480015509750729</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90880750490873041</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.69218443980071798</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.37094784017606774</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.12287387076067158</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-D6A7-4E70-B359-34E971E449B7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1798725487"/>
+        <c:axId val="1798721647"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1798725487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="8"/>
+          <c:min val="4"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>At Least This Many</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Balls</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.40292116940690825"/>
+              <c:y val="0.82991432304054324"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1798721647"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1798721647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Chance of Success</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1798725487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.15446515663452939"/>
+          <c:y val="0.89878726749215632"/>
+          <c:w val="0.71140005250677141"/>
+          <c:h val="8.18187857098681E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -24793,6 +26044,86 @@
 </file>
 
 <file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -26701,6 +28032,1038 @@
 </file>
 
 <file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -31838,16 +34201,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>414337</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>433388</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>109537</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>600076</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -31903,6 +34266,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8942F0D6-8E97-D6FE-88B0-8473710CEF78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>414338</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>504826</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>57149</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84460245-F57E-826B-C245-CF15E967C321}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -58350,16 +60785,16 @@
       </c>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E22" s="53" t="s">
+      <c r="E22" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
     </row>
     <row r="23" spans="2:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="20"/>
@@ -58657,18 +61092,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="H2" s="54" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="H2" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
     </row>
     <row r="3" spans="2:13" ht="9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C3"/>
@@ -58740,18 +61175,18 @@
     </row>
     <row r="8" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="63" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="H10" s="54" t="s">
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="H10" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
       <c r="L10" s="35"/>
       <c r="M10" s="35"/>
     </row>
@@ -58837,18 +61272,18 @@
       </c>
     </row>
     <row r="17" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="54"/>
-      <c r="D17" s="54"/>
-      <c r="E17" s="54"/>
-      <c r="H17" s="54" t="s">
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="H17" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="54"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="54"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" spans="2:11" ht="9" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B18" s="42"/>
@@ -58918,12 +61353,12 @@
       </c>
     </row>
     <row r="24" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
@@ -59247,17 +61682,17 @@
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
-      <c r="I23" s="55"/>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
     </row>
     <row r="24" spans="1:9" s="14" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
@@ -70350,19 +72785,19 @@
         <v>109</v>
       </c>
       <c r="K1" s="10"/>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="M1" s="56" t="s">
+      <c r="M1" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="N1" s="57" t="s">
+      <c r="N1" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="O1" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="P1" s="57"/>
+      <c r="P1" s="54"/>
       <c r="Q1" s="48" t="s">
         <v>114</v>
       </c>
@@ -71139,140 +73574,148 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5F652A-E5E7-49FD-81C7-54888FFB9D2C}">
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" style="59" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" style="59" customWidth="1"/>
-    <col min="4" max="5" width="9.28515625" style="59" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="62"/>
-    <col min="7" max="16384" width="9.140625" style="59"/>
+    <col min="1" max="1" width="9.28515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="56" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="56" customWidth="1"/>
+    <col min="4" max="5" width="9.28515625" style="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="59"/>
+    <col min="7" max="20" width="9.140625" style="56"/>
+    <col min="21" max="21" width="10.28515625" style="56" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="57" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:23" s="54" customFormat="1" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="E1" s="57" t="s">
+      <c r="E1" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="57" t="s">
+      <c r="G1" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="H1" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
-      <c r="P1" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="64"/>
-      <c r="S1" s="64"/>
-      <c r="T1" s="64"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
       <c r="V1" s="50" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" s="57" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="W1" s="50" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" s="54" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="60"/>
-      <c r="G2" s="57" t="s">
+      <c r="F2" s="57"/>
+      <c r="G2" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="H2" s="57">
+      <c r="H2" s="54">
         <v>4</v>
       </c>
-      <c r="I2" s="57">
+      <c r="I2" s="54">
         <v>5</v>
       </c>
-      <c r="J2" s="57">
+      <c r="J2" s="54">
         <v>6</v>
       </c>
-      <c r="K2" s="57">
+      <c r="K2" s="54">
         <v>7</v>
       </c>
-      <c r="L2" s="57">
+      <c r="L2" s="54">
         <v>8</v>
       </c>
-      <c r="M2" s="57">
+      <c r="M2" s="54">
         <v>9</v>
       </c>
-      <c r="N2" s="57">
+      <c r="N2" s="54">
         <v>10</v>
       </c>
-      <c r="O2" s="57">
+      <c r="O2" s="54">
         <v>11</v>
       </c>
-      <c r="P2" s="57">
+      <c r="P2" s="54">
         <v>4</v>
       </c>
-      <c r="Q2" s="57">
+      <c r="Q2" s="54">
         <v>5</v>
       </c>
-      <c r="R2" s="57">
+      <c r="R2" s="54">
         <v>6</v>
       </c>
-      <c r="S2" s="57">
+      <c r="S2" s="54">
         <v>7</v>
       </c>
-      <c r="T2" s="57">
+      <c r="T2" s="54">
         <v>8</v>
       </c>
-      <c r="V2" s="63">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="58">
+      <c r="V2" s="60">
+        <v>11.5</v>
+      </c>
+      <c r="W2" s="50">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="55">
         <v>0.4</v>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="55">
         <v>28.2021151586369</v>
       </c>
-      <c r="C3" s="59">
+      <c r="C3" s="56">
         <v>4.8354054051736526</v>
       </c>
-      <c r="D3" s="59">
+      <c r="D3" s="56">
         <v>67.769230769230774</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="56">
         <v>10.207086527732368</v>
       </c>
-      <c r="F3" s="61">
+      <c r="F3" s="58">
         <f>_xlfn.NORM.DIST(21.385, 0, E3, TRUE) - _xlfn.NORM.DIST(-21.385, 0, E3, TRUE)</f>
         <v>0.96383905423860639</v>
       </c>
@@ -71280,76 +73723,76 @@
         <f>F3*B3</f>
         <v>27.182300002028853</v>
       </c>
-      <c r="H3" s="59">
-        <f>1 - _xlfn.NORM.DIST(H$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>0.9696770380530364</v>
-      </c>
-      <c r="I3" s="59">
-        <f>1 - _xlfn.NORM.DIST(I$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>0.8178639838723013</v>
-      </c>
-      <c r="J3" s="59">
-        <f>1 - _xlfn.NORM.DIST(J$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>0.47545725518320481</v>
-      </c>
-      <c r="K3" s="59">
-        <f>1 - _xlfn.NORM.DIST(K$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>0.15141778534535955</v>
-      </c>
-      <c r="L3" s="59">
-        <f>1 - _xlfn.NORM.DIST(L$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>2.2794174302502523E-2</v>
-      </c>
-      <c r="M3" s="59">
-        <f>1 - _xlfn.NORM.DIST(M$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>1.4987304482405595E-3</v>
-      </c>
-      <c r="N3" s="59">
-        <f>1 - _xlfn.NORM.DIST(N$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>4.1285714419192487E-5</v>
-      </c>
-      <c r="O3" s="59">
-        <f>1 - _xlfn.NORM.DIST(O$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
-        <v>4.6565217448613083E-7</v>
-      </c>
-      <c r="P3" s="59">
-        <f>IF(P$2 &gt; 8, 0, 1 - _xlfn.NORM.DIST(P$2 - 0.5, MIN(8, ($B3/60)*$V$2)*$F3, SQRT(MIN(8, ($B3/60)*$V$2)*$F3*(1-$F3) + (($C3/60)*$V$2 * _xlfn.NORM.DIST(8, ($B3/60)*$V$2, ($C3/60)*$V$2, TRUE) * $F3)^2), TRUE))</f>
-        <v>0.97044446881937951</v>
-      </c>
-      <c r="Q3" s="59">
-        <f t="shared" ref="Q3:T7" si="0">IF(Q$2 &gt; 8, 0, 1 - _xlfn.NORM.DIST(Q$2 - 0.5, MIN(8, ($B3/60)*$V$2)*$F3, SQRT(MIN(8, ($B3/60)*$V$2)*$F3*(1-$F3) + (($C3/60)*$V$2 * _xlfn.NORM.DIST(8, ($B3/60)*$V$2, ($C3/60)*$V$2, TRUE) * $F3)^2), TRUE))</f>
-        <v>0.81930473013074911</v>
-      </c>
-      <c r="R3" s="59">
+      <c r="H3" s="65">
+        <f t="shared" ref="H3:O7" si="0">1 - _xlfn.NORM.DIST(H$2 - 0.5, ($B3/60)*$V$2*$F3, SQRT((($B3/60)*$V$2*$F3*(1-$F3)) + (($C3/60)*$V$2*$F3)^2), TRUE)</f>
+        <v>0.9574423650561259</v>
+      </c>
+      <c r="I3" s="65">
         <f t="shared" si="0"/>
-        <v>0.4753096396248111</v>
-      </c>
-      <c r="S3" s="59">
+        <v>0.76264689978251732</v>
+      </c>
+      <c r="J3" s="65">
         <f t="shared" si="0"/>
-        <v>0.14996654820944189</v>
-      </c>
-      <c r="T3" s="59">
+        <v>0.38511963186167564</v>
+      </c>
+      <c r="K3" s="65">
         <f t="shared" si="0"/>
-        <v>2.2150867841099653E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="58">
+        <v>9.6977685364832422E-2</v>
+      </c>
+      <c r="L3" s="65">
+        <f t="shared" si="0"/>
+        <v>1.0558910144791489E-2</v>
+      </c>
+      <c r="M3" s="65">
+        <f t="shared" si="0"/>
+        <v>4.6187449682422166E-4</v>
+      </c>
+      <c r="N3" s="65">
+        <f t="shared" si="0"/>
+        <v>7.8127518212678382E-6</v>
+      </c>
+      <c r="O3" s="65">
+        <f t="shared" si="0"/>
+        <v>5.0038082455294841E-8</v>
+      </c>
+      <c r="P3" s="65">
+        <f>IF(P$2 &gt; $W$2, 0, 1 - _xlfn.NORM.DIST(P$2 - 0.5, MIN($W$2, ($B3/60)*$V$2)*$F3, SQRT(MIN($W$2, ($B3/60)*$V$2)*$F3*(1-$F3) + (($C3/60)*$V$2 * _xlfn.NORM.DIST($W$2, ($B3/60)*$V$2, ($C3/60)*$V$2, TRUE) * $F3)^2), TRUE))</f>
+        <v>0.95776489564622558</v>
+      </c>
+      <c r="Q3" s="65">
+        <f t="shared" ref="Q3:T7" si="1">IF(Q$2 &gt; $W$2, 0, 1 - _xlfn.NORM.DIST(Q$2 - 0.5, MIN($W$2, ($B3/60)*$V$2)*$F3, SQRT(MIN($W$2, ($B3/60)*$V$2)*$F3*(1-$F3) + (($C3/60)*$V$2 * _xlfn.NORM.DIST($W$2, ($B3/60)*$V$2, ($C3/60)*$V$2, TRUE) * $F3)^2), TRUE))</f>
+        <v>0.76310469259575797</v>
+      </c>
+      <c r="R3" s="65">
+        <f t="shared" si="1"/>
+        <v>0.38488812450584486</v>
+      </c>
+      <c r="S3" s="65">
+        <f t="shared" si="1"/>
+        <v>9.6516268768836566E-2</v>
+      </c>
+      <c r="T3" s="65">
+        <f t="shared" si="1"/>
+        <v>1.0426014367353909E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="55">
         <v>0.5</v>
       </c>
-      <c r="B4" s="58">
+      <c r="B4" s="55">
         <v>43.082446467495828</v>
       </c>
-      <c r="C4" s="59">
+      <c r="C4" s="56">
         <v>5.969998426907047</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="56">
         <v>68.5311004784689</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="56">
         <v>10.788626455779969</v>
       </c>
-      <c r="F4" s="61">
+      <c r="F4" s="58">
         <f>_xlfn.NORM.DIST(21.385, 0, E4, TRUE) - _xlfn.NORM.DIST(-21.385, 0, E4, TRUE)</f>
         <v>0.95254090598405416</v>
       </c>
@@ -71357,76 +73800,76 @@
         <f>F4*B4</f>
         <v>41.037792590157991</v>
       </c>
-      <c r="H4" s="59">
-        <f>1 - _xlfn.NORM.DIST(H$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>0.9998575557358953</v>
-      </c>
-      <c r="I4" s="59">
-        <f>1 - _xlfn.NORM.DIST(I$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>0.99786738849815315</v>
-      </c>
-      <c r="J4" s="59">
-        <f>1 - _xlfn.NORM.DIST(J$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>0.98155740535277414</v>
-      </c>
-      <c r="K4" s="59">
-        <f>1 - _xlfn.NORM.DIST(K$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>0.90594912479252632</v>
-      </c>
-      <c r="L4" s="59">
-        <f>1 - _xlfn.NORM.DIST(L$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>0.70726017866051094</v>
-      </c>
-      <c r="M4" s="59">
-        <f>1 - _xlfn.NORM.DIST(M$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>0.41082669937819594</v>
-      </c>
-      <c r="N4" s="59">
-        <f>1 - _xlfn.NORM.DIST(N$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>0.15956772632623006</v>
-      </c>
-      <c r="O4" s="59">
-        <f>1 - _xlfn.NORM.DIST(O$2 - 0.5, ($B4/60)*$V$2*$F4, SQRT((($B4/60)*$V$2*$F4*(1-$F4)) + (($C4/60)*$V$2*$F4)^2), TRUE)</f>
-        <v>3.8609655724096026E-2</v>
-      </c>
-      <c r="P4" s="59">
-        <f>IF(P$2 &gt; 8, 0, 1 - _xlfn.NORM.DIST(P$2 - 0.5, MIN(8, ($B4/60)*$V$2)*$F4, SQRT(MIN(8, ($B4/60)*$V$2)*$F4*(1-$F4) + (($C4/60)*$V$2 * _xlfn.NORM.DIST(8, ($B4/60)*$V$2, ($C4/60)*$V$2, TRUE) * $F4)^2), TRUE))</f>
-        <v>0.99999999862221001</v>
-      </c>
-      <c r="Q4" s="59">
+      <c r="H4" s="65">
         <f t="shared" si="0"/>
-        <v>0.99999664296948976</v>
-      </c>
-      <c r="R4" s="59">
+        <v>0.99976193168754013</v>
+      </c>
+      <c r="I4" s="65">
         <f t="shared" si="0"/>
-        <v>0.9988917672105494</v>
-      </c>
-      <c r="S4" s="59">
+        <v>0.99646490236845398</v>
+      </c>
+      <c r="J4" s="65">
         <f t="shared" si="0"/>
-        <v>0.94701825281219409</v>
-      </c>
-      <c r="T4" s="59">
+        <v>0.97083471612114924</v>
+      </c>
+      <c r="K4" s="65">
         <f t="shared" si="0"/>
-        <v>0.56892161146072384</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="58">
+        <v>0.86277914978388326</v>
+      </c>
+      <c r="L4" s="65">
+        <f t="shared" si="0"/>
+        <v>0.61507705268633983</v>
+      </c>
+      <c r="M4" s="65">
+        <f t="shared" si="0"/>
+        <v>0.30581856483384795</v>
+      </c>
+      <c r="N4" s="65">
+        <f t="shared" si="0"/>
+        <v>9.5427771665146377E-2</v>
+      </c>
+      <c r="O4" s="65">
+        <f t="shared" si="0"/>
+        <v>1.7499636483525483E-2</v>
+      </c>
+      <c r="P4" s="65">
+        <f t="shared" ref="P4:P7" si="2">IF(P$2 &gt; $W$2, 0, 1 - _xlfn.NORM.DIST(P$2 - 0.5, MIN($W$2, ($B4/60)*$V$2)*$F4, SQRT(MIN($W$2, ($B4/60)*$V$2)*$F4*(1-$F4) + (($C4/60)*$V$2 * _xlfn.NORM.DIST($W$2, ($B4/60)*$V$2, ($C4/60)*$V$2, TRUE) * $F4)^2), TRUE))</f>
+        <v>0.99999998042874794</v>
+      </c>
+      <c r="Q4" s="65">
+        <f t="shared" si="1"/>
+        <v>0.99998416573569204</v>
+      </c>
+      <c r="R4" s="65">
+        <f t="shared" si="1"/>
+        <v>0.99765486328282693</v>
+      </c>
+      <c r="S4" s="65">
+        <f t="shared" si="1"/>
+        <v>0.93241434778982812</v>
+      </c>
+      <c r="T4" s="65">
+        <f t="shared" si="1"/>
+        <v>0.56374175516638803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="55">
         <v>0.6</v>
       </c>
-      <c r="B5" s="58">
+      <c r="B5" s="55">
         <v>43.807040417209905</v>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="56">
         <v>7.8663086701593627</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="56">
         <v>65.115384615384613</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="56">
         <v>12.113882690787202</v>
       </c>
-      <c r="F5" s="61">
+      <c r="F5" s="58">
         <f>_xlfn.NORM.DIST(21.385, 0, E5, TRUE) - _xlfn.NORM.DIST(-21.385, 0, E5, TRUE)</f>
         <v>0.92249167226534112</v>
       </c>
@@ -71434,76 +73877,76 @@
         <f>F5*B5</f>
         <v>40.411629971467349</v>
       </c>
-      <c r="H5" s="59">
-        <f>1 - _xlfn.NORM.DIST(H$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>0.99721382589622964</v>
-      </c>
-      <c r="I5" s="59">
-        <f>1 - _xlfn.NORM.DIST(I$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>0.98488331019823538</v>
-      </c>
-      <c r="J5" s="59">
-        <f>1 - _xlfn.NORM.DIST(J$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>0.94086774842981069</v>
-      </c>
-      <c r="K5" s="59">
-        <f>1 - _xlfn.NORM.DIST(K$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>0.83076181147788397</v>
-      </c>
-      <c r="L5" s="59">
-        <f>1 - _xlfn.NORM.DIST(L$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>0.63767851909881701</v>
-      </c>
-      <c r="M5" s="59">
-        <f>1 - _xlfn.NORM.DIST(M$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>0.40026578640053534</v>
-      </c>
-      <c r="N5" s="59">
-        <f>1 - _xlfn.NORM.DIST(N$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>0.19556253053496242</v>
-      </c>
-      <c r="O5" s="59">
-        <f>1 - _xlfn.NORM.DIST(O$2 - 0.5, ($B5/60)*$V$2*$F5, SQRT((($B5/60)*$V$2*$F5*(1-$F5)) + (($C5/60)*$V$2*$F5)^2), TRUE)</f>
-        <v>7.1802330189202901E-2</v>
-      </c>
-      <c r="P5" s="59">
-        <f t="shared" ref="P5:P7" si="1">IF(P$2 &gt; 8, 0, 1 - _xlfn.NORM.DIST(P$2 - 0.5, MIN(8, ($B5/60)*$V$2)*$F5, SQRT(MIN(8, ($B5/60)*$V$2)*$F5*(1-$F5) + (($C5/60)*$V$2 * _xlfn.NORM.DIST(8, ($B5/60)*$V$2, ($C5/60)*$V$2, TRUE) * $F5)^2), TRUE))</f>
-        <v>0.99999441767274566</v>
-      </c>
-      <c r="Q5" s="59">
+      <c r="H5" s="65">
         <f t="shared" si="0"/>
-        <v>0.99944486352628725</v>
-      </c>
-      <c r="R5" s="59">
+        <v>0.99616920333634418</v>
+      </c>
+      <c r="I5" s="65">
         <f t="shared" si="0"/>
-        <v>0.98335921560388095</v>
-      </c>
-      <c r="S5" s="59">
+        <v>0.97925161829567231</v>
+      </c>
+      <c r="J5" s="65">
         <f t="shared" si="0"/>
-        <v>0.84046203420457932</v>
-      </c>
-      <c r="T5" s="59">
+        <v>0.92079417474301772</v>
+      </c>
+      <c r="K5" s="65">
         <f t="shared" si="0"/>
-        <v>0.44592929414890059</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="58">
+        <v>0.78299129207556029</v>
+      </c>
+      <c r="L5" s="65">
+        <f t="shared" si="0"/>
+        <v>0.56128868796288511</v>
+      </c>
+      <c r="M5" s="65">
+        <f t="shared" si="0"/>
+        <v>0.31779955157294304</v>
+      </c>
+      <c r="N5" s="65">
+        <f t="shared" si="0"/>
+        <v>0.13523972413647023</v>
+      </c>
+      <c r="O5" s="65">
+        <f t="shared" si="0"/>
+        <v>4.1810017112676512E-2</v>
+      </c>
+      <c r="P5" s="65">
+        <f t="shared" si="2"/>
+        <v>0.99998306884080768</v>
+      </c>
+      <c r="Q5" s="65">
+        <f t="shared" si="1"/>
+        <v>0.99895550363432284</v>
+      </c>
+      <c r="R5" s="65">
+        <f t="shared" si="1"/>
+        <v>0.9777184389137954</v>
+      </c>
+      <c r="S5" s="65">
+        <f t="shared" si="1"/>
+        <v>0.82645031316347495</v>
+      </c>
+      <c r="T5" s="65">
+        <f t="shared" si="1"/>
+        <v>0.44895810295391736</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" s="55">
         <v>0.75</v>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="55">
         <v>53.063802905874915</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="56">
         <v>10.876230117440507</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="56">
         <v>56.666666666666664</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="56">
         <v>14.803845654215872</v>
       </c>
-      <c r="F6" s="61">
+      <c r="F6" s="58">
         <f>_xlfn.NORM.DIST(21.385, 0, E6, TRUE) - _xlfn.NORM.DIST(-21.385, 0, E6, TRUE)</f>
         <v>0.85141766323462797</v>
       </c>
@@ -71511,76 +73954,76 @@
         <f>F6*B6</f>
         <v>45.179459072462883</v>
       </c>
-      <c r="H6" s="59">
-        <f>1 - _xlfn.NORM.DIST(H$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.99436173167040132</v>
-      </c>
-      <c r="I6" s="59">
-        <f>1 - _xlfn.NORM.DIST(I$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.9810654333089136</v>
-      </c>
-      <c r="J6" s="59">
-        <f>1 - _xlfn.NORM.DIST(J$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.947225394726251</v>
-      </c>
-      <c r="K6" s="59">
-        <f>1 - _xlfn.NORM.DIST(K$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.87713518796685108</v>
-      </c>
-      <c r="L6" s="59">
-        <f>1 - _xlfn.NORM.DIST(L$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.75898529465477549</v>
-      </c>
-      <c r="M6" s="59">
-        <f>1 - _xlfn.NORM.DIST(M$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.59688800801258424</v>
-      </c>
-      <c r="N6" s="59">
-        <f>1 - _xlfn.NORM.DIST(N$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.41588117688931692</v>
-      </c>
-      <c r="O6" s="59">
-        <f>1 - _xlfn.NORM.DIST(O$2 - 0.5, ($B6/60)*$V$2*$F6, SQRT((($B6/60)*$V$2*$F6*(1-$F6)) + (($C6/60)*$V$2*$F6)^2), TRUE)</f>
-        <v>0.25137028951317109</v>
-      </c>
-      <c r="P6" s="59">
+      <c r="H6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.99284568524933581</v>
+      </c>
+      <c r="I6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.97584725533361616</v>
+      </c>
+      <c r="J6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.93318264686627428</v>
+      </c>
+      <c r="K6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.84735902525244522</v>
+      </c>
+      <c r="L6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.70898527594515315</v>
+      </c>
+      <c r="M6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.53016049631633466</v>
+      </c>
+      <c r="N6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.34491855788538306</v>
+      </c>
+      <c r="O6" s="65">
+        <f t="shared" si="0"/>
+        <v>0.19110662977978254</v>
+      </c>
+      <c r="P6" s="65">
+        <f t="shared" si="2"/>
+        <v>0.99927266981581164</v>
+      </c>
+      <c r="Q6" s="65">
         <f t="shared" si="1"/>
-        <v>0.99935989518896995</v>
-      </c>
-      <c r="Q6" s="59">
-        <f t="shared" si="0"/>
-        <v>0.98770710064365752</v>
-      </c>
-      <c r="R6" s="59">
-        <f t="shared" si="0"/>
-        <v>0.89890183767130794</v>
-      </c>
-      <c r="S6" s="59">
-        <f t="shared" si="0"/>
-        <v>0.6189746047304393</v>
-      </c>
-      <c r="T6" s="59">
-        <f t="shared" si="0"/>
-        <v>0.25151132404853804</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="58">
+        <v>0.98686384629681678</v>
+      </c>
+      <c r="R6" s="65">
+        <f t="shared" si="1"/>
+        <v>0.89629977543798078</v>
+      </c>
+      <c r="S6" s="65">
+        <f t="shared" si="1"/>
+        <v>0.61765541546167335</v>
+      </c>
+      <c r="T6" s="65">
+        <f t="shared" si="1"/>
+        <v>0.25395736171909966</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" s="55">
         <v>1</v>
       </c>
-      <c r="B7" s="58">
+      <c r="B7" s="55">
         <v>70.48458149779735</v>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="56">
         <v>9.1508649349417936</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="56">
         <v>41.769230769230766</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="56">
         <v>18.084927851241634</v>
       </c>
-      <c r="F7" s="61">
+      <c r="F7" s="58">
         <f>_xlfn.NORM.DIST(21.385, 0, E7, TRUE) - _xlfn.NORM.DIST(-21.385, 0, E7, TRUE)</f>
         <v>0.76298326735887789</v>
       </c>
@@ -71588,57 +74031,82 @@
         <f>F7*B7</f>
         <v>53.778556289612531</v>
       </c>
-      <c r="H7" s="59">
-        <f>1 - _xlfn.NORM.DIST(H$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.99968767844300088</v>
-      </c>
-      <c r="I7" s="59">
-        <f>1 - _xlfn.NORM.DIST(I$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.99840719297168368</v>
-      </c>
-      <c r="J7" s="59">
-        <f>1 - _xlfn.NORM.DIST(J$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.99339002398426668</v>
-      </c>
-      <c r="K7" s="59">
-        <f>1 - _xlfn.NORM.DIST(K$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.97759009132379082</v>
-      </c>
-      <c r="L7" s="59">
-        <f>1 - _xlfn.NORM.DIST(L$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.93759515775908497</v>
-      </c>
-      <c r="M7" s="59">
-        <f>1 - _xlfn.NORM.DIST(M$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.85621056380417648</v>
-      </c>
-      <c r="N7" s="59">
-        <f>1 - _xlfn.NORM.DIST(N$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.72307507054919617</v>
-      </c>
-      <c r="O7" s="59">
-        <f>1 - _xlfn.NORM.DIST(O$2 - 0.5, ($B7/60)*$V$2*$F7, SQRT((($B7/60)*$V$2*$F7*(1-$F7)) + (($C7/60)*$V$2*$F7)^2), TRUE)</f>
-        <v>0.54797795069060573</v>
-      </c>
-      <c r="P7" s="59">
-        <f>IF(P$2 &gt; 8, 0, 1 - _xlfn.NORM.DIST(P$2 - 0.5, MIN(8, ($B7/60)*$V$2)*$F7, SQRT(MIN(8, ($B7/60)*$V$2)*$F7*(1-$F7) + (($C7/60)*$V$2 * _xlfn.NORM.DIST(8, ($B7/60)*$V$2, ($C7/60)*$V$2, TRUE) * $F7)^2), TRUE))</f>
-        <v>0.98480018096413346</v>
-      </c>
-      <c r="Q7" s="59">
+      <c r="H7" s="65">
         <f t="shared" si="0"/>
-        <v>0.90880757311972948</v>
-      </c>
-      <c r="R7" s="59">
+        <v>0.99953090708594905</v>
+      </c>
+      <c r="I7" s="65">
         <f t="shared" si="0"/>
-        <v>0.69218449488142098</v>
-      </c>
-      <c r="S7" s="59">
+        <v>0.99761702398908125</v>
+      </c>
+      <c r="J7" s="65">
         <f t="shared" si="0"/>
-        <v>0.37094780135382543</v>
-      </c>
-      <c r="T7" s="59">
-        <f>IF(T$2 &gt; 8, 0, 1 - _xlfn.NORM.DIST(T$2 - 0.5, MIN(8, ($B7/60)*$V$2)*$F7, SQRT(MIN(8, ($B7/60)*$V$2)*$F7*(1-$F7) + (($C7/60)*$V$2 * _xlfn.NORM.DIST(8, ($B7/60)*$V$2, ($C7/60)*$V$2, TRUE) * $F7)^2), TRUE))</f>
-        <v>0.12287379711403668</v>
+        <v>0.99026601686269577</v>
+      </c>
+      <c r="K7" s="65">
+        <f t="shared" si="0"/>
+        <v>0.96787579673055801</v>
+      </c>
+      <c r="L7" s="65">
+        <f t="shared" si="0"/>
+        <v>0.913788190804529</v>
+      </c>
+      <c r="M7" s="65">
+        <f t="shared" si="0"/>
+        <v>0.81015370663288144</v>
+      </c>
+      <c r="N7" s="65">
+        <f t="shared" si="0"/>
+        <v>0.65264384891716254</v>
+      </c>
+      <c r="O7" s="65">
+        <f t="shared" si="0"/>
+        <v>0.46274266772157913</v>
+      </c>
+      <c r="P7" s="65">
+        <f t="shared" si="2"/>
+        <v>0.98480015509750729</v>
+      </c>
+      <c r="Q7" s="65">
+        <f t="shared" si="1"/>
+        <v>0.90880750490873041</v>
+      </c>
+      <c r="R7" s="65">
+        <f t="shared" si="1"/>
+        <v>0.69218443980071798</v>
+      </c>
+      <c r="S7" s="65">
+        <f t="shared" si="1"/>
+        <v>0.37094784017606774</v>
+      </c>
+      <c r="T7" s="65">
+        <f t="shared" si="1"/>
+        <v>0.12287387076067158</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U11" s="56" t="s">
+        <v>126</v>
+      </c>
+      <c r="V11" s="56">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U12" s="56" t="s">
+        <v>127</v>
+      </c>
+      <c r="V12" s="56">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="U16" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="V16" s="56">
+        <f>20-SUM(V11:V15)</f>
+        <v>7.8000000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -71646,6 +74114,16 @@
     <mergeCell ref="H1:O1"/>
     <mergeCell ref="P1:T1"/>
   </mergeCells>
+  <conditionalFormatting sqref="H3:T7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
